--- a/docs/同棲から子育てまでのWBS.xlsx
+++ b/docs/同棲から子育てまでのWBS.xlsx
@@ -766,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1131,61 +1131,68 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>・フェーズの期間はあくまで標準モデル。特に妊活（P8）は個人差が大きく、数ヶ月〜数年の幅がある。①の黄色いセルを実態に合わせて書き換えて使う。</t>
+          <t>・P15〜P18の境目は「4月の入学・進級」に合わせてある。これは基準日2026年10月（＝出産2029年11月）の場合の月数なので、実際の出産月がずれたら①の開始（経過月）を入学年度に合わせて調整すること。小学校入学は「4月1日までに6歳になった年の4月」。</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>・妊活・妊娠の時期を後ろにずらすと、その後のフェーズも全部後ろにずれる。年齢と妊娠率の関係があるため、結婚式と妊活の順番は意識的に決める。</t>
+          <t>・フェーズの期間はあくまで標準モデル。特に妊活（P8）は個人差が大きく、数ヶ月〜数年の幅がある。①の黄色いセルを実態に合わせて書き換えて使う。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>・費用は目安であり、地域・式場・産院・治療内容で大きく変わる。ご祝儀・親の援助・出産育児一時金50万円・児童手当・育児休業給付金は差し引く前の金額。</t>
+          <t>・妊活・妊娠の時期を後ろにずらすと、その後のフェーズも全部後ろにずれる。年齢と妊娠率の関係があるため、結婚式と妊活の順番は意識的に決める。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>・制度は2026年8月時点。RSV母子免疫ワクチンの定期接種化（2026年4月〜）、こども誰でも通園制度（2026年4月〜）、出生後休業支援給付金、育児時短就業給付を反映。出産費用の保険適用化は2027〜2028年度の見込みのため、出産育児一時金50万円を前提にしている。</t>
+          <t>・費用は目安であり、地域・式場・産院・治療内容で大きく変わる。ご祝儀・親の援助・出産育児一時金50万円・児童手当・育児休業給付金は差し引く前の金額。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>・助成の金額・回数・申請時期は自治体差が非常に大きい。必ず住んでいる市区町村の公式情報で確認すること。</t>
+          <t>・制度は2026年8月時点。RSV母子免疫ワクチンの定期接種化（2026年4月〜）、こども誰でも通園制度（2026年4月〜）、出生後休業支援給付金、育児時短就業給付を反映。出産費用の保険適用化は2027〜2028年度の見込みのため、出産育児一時金50万円を前提にしている。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>・本表は計画テンプレートであり、医療上の助言ではない。健康・治療・接種の判断は主治医に、制度の適用可否は自治体・健保・勤務先・ハローワークに確認すること。</t>
+          <t>・助成の金額・回数・申請時期は自治体差が非常に大きい。必ず住んでいる市区町村の公式情報で確認すること。</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>・商品・サービス名は2026年8月時点で一般に流通している選択肢の例であり、特定の推奨ではない。価格と仕様は必ず最新の情報を確認すること。</t>
+          <t>・本表は計画テンプレートであり、医療上の助言ではない。健康・治療・接種の判断は主治医に、制度の適用可否は自治体・健保・勤務先・ハローワークに確認すること。</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
         <is>
+          <t>・商品・サービス名は2026年8月時点で一般に流通している選択肢の例であり、特定の推奨ではない。価格と仕様は必ず最新の情報を確認すること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
           <t>・③リスク管理表の確率・影響の初期値は一般的な想定値。2人の実感に合わせて必ず書き換えること。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="C24:G24"/>
@@ -1199,6 +1206,7 @@
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C9:G9"/>
+    <mergeCell ref="A45:G45"/>
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="C21:G21"/>
     <mergeCell ref="C11:G11"/>
@@ -3712,7 +3720,7 @@
       </c>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t>保育園との生活リズムが回り、イヤイヤ期を2人で乗り切れている状態</t>
+          <t>保育園と家庭の生活リズムが安定し、イヤイヤ期を「2人で同じ方針」で乗り切れている状態</t>
         </is>
       </c>
       <c r="E17" s="26" t="n">
@@ -3735,12 +3743,12 @@
       </c>
       <c r="J17" s="25" t="inlineStr">
         <is>
-          <t>公園デビュー／1歳6ヶ月健診／卒乳・断乳／歩行と発語／イヤイヤ期／2歳の誕生日／トイレトレーニング開始</t>
+          <t>公園デビュー／1歳6ヶ月児健診／卒乳・断乳／歩行と発語／イヤイヤ期（1歳半頃〜）／トイレトレーニング開始／2歳の誕生日</t>
         </is>
       </c>
       <c r="K17" s="25" t="inlineStr">
         <is>
-          <t>習い事を始めるか（ベビースイミング・リトミック・体操）／2人目をいつにするか／叱り方の方針を2人で揃えるか／転園・引っ越しの要否／テレビと動画のルール</t>
+          <t>習い事を始めるか（ベビースイミング・リトミック・幼児教室）／2人目をいつにするか（産休・育休の再設計込みで）／叱り方・生活ルールを2人で揃える／テレビ・動画・スマホのルール／転園・引っ越しの要否</t>
         </is>
       </c>
       <c r="L17" s="26" t="n">
@@ -3751,7 +3759,7 @@
       </c>
       <c r="N17" s="25" t="inlineStr">
         <is>
-          <t>イヤイヤ期の対応方針が食い違い、「甘い／厳しい」と互いを責め合う</t>
+          <t>イヤイヤ期の対応で「甘い／厳しい」と互いを責め、子どもの前で対立する</t>
         </is>
       </c>
       <c r="O17" s="29" t="inlineStr">
@@ -3768,21 +3776,21 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>3〜5歳（就学前）</t>
+          <t>就学前（3〜5歳児クラス）</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>3〜5歳</t>
+          <t>3〜6歳</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>小学校の選択が決まり、就学に向けた生活習慣がついている状態</t>
+          <t>小学校の進路（公立か国私立か）が決まり、就学に耐える生活習慣がついている状態</t>
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F18" s="26" t="n">
         <v>73</v>
@@ -3801,12 +3809,12 @@
       </c>
       <c r="J18" s="25" t="inlineStr">
         <is>
-          <t>3歳児健診／幼児教育・保育の無償化開始（3歳児クラスから）／七五三／習い事の本格スタート／ラン活（年長の春〜夏）／就学時健診（年長の10〜11月）／学童の申込（年長の11〜12月）</t>
+          <t>3歳児健診／幼児教育・保育の無償化（3歳児クラス〜）／七五三／習い事の本格開始／ラン活（年長の春〜夏）／就学時健診（年長の10〜11月）／学童の申込（年長の秋〜冬）</t>
         </is>
       </c>
       <c r="K18" s="25" t="inlineStr">
         <is>
-          <t>保育園を続けるか幼稚園に移るか／習い事を何にするか（スイミング・ピアノ・体操・英語・サッカー・そろばん）／小学校は公立か国私立か／学区のために引っ越すか／2人目の結論／教育費の積立額の見直し</t>
+          <t>保育園を続けるか幼稚園（預かり保育あり）に移るか／習い事の選択と数の上限（スイミング・ピアノ・体操・英語・そろばん）／小学校は公立か国私立か（受験するなら準備は年中から）／学区のための引っ越し／2人目の結論／教育費の積立額の見直し</t>
         </is>
       </c>
       <c r="L18" s="26" t="n">
@@ -3817,7 +3825,7 @@
       </c>
       <c r="N18" s="25" t="inlineStr">
         <is>
-          <t>習い事を増やしすぎて、子どもの時間と家計の両方が破綻する</t>
+          <t>習い事を増やしすぎて、子どもの自由時間・家計・送迎の全部が回らなくなる</t>
         </is>
       </c>
       <c r="O18" s="29" t="inlineStr">
@@ -3834,24 +3842,24 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>小学校 低学年（6〜8歳）</t>
+          <t>小学校 低学年（小1〜小3）</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>6〜8歳</t>
+          <t>6〜9歳</t>
         </is>
       </c>
       <c r="D19" s="25" t="inlineStr">
         <is>
-          <t>学校と学童のリズムが回り、家庭学習の習慣がついている状態</t>
+          <t>小1の壁を越えて学校・学童・仕事のリズムが回り、家庭学習が習慣になっている状態</t>
         </is>
       </c>
       <c r="E19" s="26" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F19" s="26" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G19" s="27">
         <f>F19+E19-1</f>
@@ -3867,12 +3875,12 @@
       </c>
       <c r="J19" s="25" t="inlineStr">
         <is>
-          <t>小学校入学／学童スタート／PTA・保護者会／夏休みの預け先／家庭学習の習慣化／習い事の絞り込み／子ども名義の口座と積立の見直し</t>
+          <t>小学校入学／学童スタート／PTA・保護者会／長期休みの預け先確保／家庭学習の習慣化（毎日10分×学年が目安）／習い事の絞り込み</t>
         </is>
       </c>
       <c r="K19" s="25" t="inlineStr">
         <is>
-          <t>学童は公立か民間か／中学受験をするかの初期検討（小3までに方向性）／習い事を絞るか続けるか／スマホ・ゲーム・タブレットのルール／長期休みの預け先をどうするか</t>
+          <t>学童は公立か民間か（お迎え時間と長期休み対応で比較）／中学受験をするかの方向づけ（小3までに）／通信教材か塾か／スマホ・ゲームのルール／子ども名義の口座と教育費の再点検</t>
         </is>
       </c>
       <c r="L19" s="26" t="n">
@@ -3883,7 +3891,7 @@
       </c>
       <c r="N19" s="25" t="inlineStr">
         <is>
-          <t>小1の壁（学童は保育園より終わりが早く、長期休みもある）で働き方が破綻する</t>
+          <t>小1の壁（学童は保育園より閉まるのが早く、長期休みは弁当持参）で共働きの働き方が破綻する</t>
         </is>
       </c>
       <c r="O19" s="29" t="inlineStr">
@@ -3900,7 +3908,7 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>中学受験 準備期（9〜10歳｜小3冬〜小4）</t>
+          <t>中学受験 準備期（小3の2月〜小4）</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -3910,14 +3918,14 @@
       </c>
       <c r="D20" s="25" t="inlineStr">
         <is>
-          <t>受験するかの結論が出て、塾が決まり、通塾のリズムができている状態</t>
+          <t>受験する／しないの結論が出て、塾と伴走体制が決まり、通塾のリズムが回っている状態</t>
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G20" s="27">
         <f>F20+E20-1</f>
@@ -3933,12 +3941,12 @@
       </c>
       <c r="J20" s="25" t="inlineStr">
         <is>
-          <t>小3の2月＝新小4の通塾スタート（大手塾の標準）／入塾テスト／志望校の初期リストアップ／学校説明会・文化祭の見学開始／小4の学習量に生活を合わせる</t>
+          <t>小3の2月＝新小4カリキュラム開始（大手塾の標準）／入塾テスト／週2〜3日の通塾開始／志望校の初期リストアップ／学校説明会・文化祭の見学開始</t>
         </is>
       </c>
       <c r="K20" s="25" t="inlineStr">
         <is>
-          <t>中学受験をするかしないか／塾をどこにするか（SAPIX・日能研・四谷大塚・早稲田アカデミー・栄光ゼミナール・地域塾・個別指導・通信）／週何日通うか／送迎と弁当を誰が担当するか／小4〜小6の総予算の上限／親のどちらが伴走役になるか</t>
+          <t>中学受験をするかしないか（子の意思と適性を含めて）／塾の選択（SAPIX・日能研・四谷大塚・早稲田アカデミー・地域塾・個別・通信）／送迎・弁当・丸つけを誰が担うか／総予算の上限（塾代は3年総額250〜400万円が相場）／親のどちらが伴走役か</t>
         </is>
       </c>
       <c r="L20" s="26" t="n">
@@ -3949,7 +3957,7 @@
       </c>
       <c r="N20" s="25" t="inlineStr">
         <is>
-          <t>受験の是非と塾の負担配分で夫婦が対立し、子どもの前で言い争う</t>
+          <t>受験の是非と課金・伴走の負担配分で夫婦が割れ、子どもの前で言い争う</t>
         </is>
       </c>
       <c r="O20" s="29" t="inlineStr">
@@ -3966,24 +3974,24 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>中学受験 本番期（11〜12歳｜小5〜小6）</t>
+          <t>中学受験 本番期（小5〜小6）</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>11〜12歳</t>
+          <t>10〜12歳</t>
         </is>
       </c>
       <c r="D21" s="25" t="inlineStr">
         <is>
-          <t>受験を終え、進学先が決まっている状態</t>
+          <t>出願・入試・進学先決定まで走り切り、結果を家族で受け止められている状態</t>
         </is>
       </c>
       <c r="E21" s="26" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F21" s="26" t="n">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="G21" s="27">
         <f>F21+E21-1</f>
@@ -3999,12 +4007,12 @@
       </c>
       <c r="J21" s="25" t="inlineStr">
         <is>
-          <t>小5＝学習量が倍増／小6春＝志望校の決定／小6夏＝夏期講習／小6秋＝過去問・学校別対策／小6の9〜12月＝出願／2月1日〜＝入試本番／進学先決定・入学準備</t>
+          <t>小5＝学習量が倍増／小6春＝志望校決定／夏期講習・過去問開始／9〜12月＝出願準備／1月＝前受け校（埼玉・千葉）／2月1日〜＝東京・神奈川の入試本番／進学先決定・入学手続き</t>
         </is>
       </c>
       <c r="K21" s="25" t="inlineStr">
         <is>
-          <t>志望校の組み合わせ（第1志望・併願・安全校）／通学時間の上限／6年間の学費総額と大学資金とのバランス／全落ちした場合に公立をどう受け止めるか／子どもの意思をどこまで尊重するか／受験をやめる判断基準</t>
+          <t>併願戦略（第1志望・実力相応・安全校＋1月前受け）／通学時間の上限／6年間の学費総額と大学資金の両立／全落ちした場合に公立中をどう受け止めるか／受験を途中でやめる判断基準／成績と模試結果への親の距離感</t>
         </is>
       </c>
       <c r="L21" s="26" t="n">
@@ -4015,7 +4023,7 @@
       </c>
       <c r="N21" s="25" t="inlineStr">
         <is>
-          <t>成績と志望校をめぐって親子・夫婦が消耗し、家庭の空気が受験一色になる</t>
+          <t>成績と志望校をめぐって親子・夫婦が消耗し、家庭の会話が受験一色になる</t>
         </is>
       </c>
       <c r="O21" s="29" t="inlineStr">
